--- a/docs/output/CVE_20260816.xlsx
+++ b/docs/output/CVE_20260816.xlsx
@@ -552,10 +552,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+          <t>&gt;=0.19.0,&lt;0.26.0</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>0.26.0</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -588,7 +592,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] vLLM is an inference and serving engine for large language models. From 0.19.0 until 0.26.0, the /v1/completions CompletionRequest.prompt field in vllm/entrypoints/openai/completion/protocol.py accepts an unbounded list[str] or list[list[int]], prompt_to_seq() in vllm/renderers/inputs/preprocess.py and OnlineRenderer.preprocess_completion() in vllm/renderers/online_renderer.py expand every element, and vllm/entrypoints/openai/completion/serving.py creates one engine generator and response slot per prompt, allowing an authenticated API client to exhaust CPU, memory, async scheduling capacity, engine request slots, and response buffering with one request. This issue is fixed in version 0.26.0.</t>
+          <t>vLLM is an inference and serving engine for large language models. From 0.19.0 until 0.26.0, the /v1/completions CompletionRequest.prompt field in vllm/entrypoints/openai/completion/protocol.py accepts an unbounded list[str] or list[list[int]], prompt_to_seq() in vllm/renderers/inputs/preprocess.py and OnlineRenderer.preprocess_completion() in vllm/renderers/online_renderer.py expand every element, and vllm/entrypoints/openai/completion/serving.py creates one engine generator and response slot per prompt, allowing an authenticated API client to exhaust CPU, memory, async scheduling capacity, engine request slots, and response buffering with one request. This issue is fixed in version 0.26.0.</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -740,7 +744,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>20260816211223</t>
+          <t>20260817204133</t>
         </is>
       </c>
     </row>
@@ -764,7 +768,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>20260814</t>
+          <t>20260815</t>
         </is>
       </c>
     </row>
@@ -776,7 +780,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>20260816</t>
+          <t>20260817</t>
         </is>
       </c>
     </row>
@@ -892,7 +896,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -904,7 +908,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/docs/output/CVE_20260816.xlsx
+++ b/docs/output/CVE_20260816.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -616,84 +616,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CVE-2026-19918</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>gRPC</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>gRPC Authors</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>CVSS:3.1/AV:A/AC:L/PR:N/UI:N/S:U/C:L/I:L/A:L</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>20260816</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>20260816</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>[버전범위 불명확] A vulnerability has been found in SpaceX Starlink Router Gen 3 2025.11.14.mr64708.3. This affects the function get_status of the component gRPC Management Interface. The manipulation leads to improper access controls. The attack can only be initiated within the local network. The exploit has been disclosed to the public and may be used. The vendor was contacted early about this disclosure but did not respond in any way.</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>https://vuldb.com/cve/CVE-2026-19918</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>NVD</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>pypi</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>20260816211125</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -744,7 +666,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>20260817204133</t>
+          <t>20260817205333</t>
         </is>
       </c>
     </row>
@@ -884,7 +806,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -896,7 +818,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/docs/output/CVE_20260816.xlsx
+++ b/docs/output/CVE_20260816.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>vLLM is an inference and serving engine for large language models. From 0.19.0 until 0.26.0, the /v1/completions CompletionRequest.prompt field in vllm/entrypoints/openai/completion/protocol.py accepts an unbounded list[str] or list[list[int]], prompt_to_seq() in vllm/renderers/inputs/preprocess.py and OnlineRenderer.preprocess_completion() in vllm/renderers/online_renderer.py expand every element, and vllm/entrypoints/openai/completion/serving.py creates one engine generator and response slot per prompt, allowing an authenticated API client to exhaust CPU, memory, async scheduling capacity, engine request slots, and response buffering with one request. This issue is fixed in version 0.26.0.</t>
+          <t>vLLM은 대규모 언어 모델을 위한 추론 및 제공 엔진입니다. 0.19.0부터 0.26.0까지 vllm/entrypoints/openai/completion/protocol.py의 /v1/completions CompletionRequest.prompt 필드는 제한되지 않은 list[str] 또는 list[list[int]], vllm/renderers/inputs/preprocess.py의 프롬프트_to_seq() 및 OnlineRenderer.preprocess_completion()을 허용합니다. vllm/renderers/online_renderer.py는 모든 요소를 확장하고 vllm/entrypoints/openai/completion/serving.py는 프롬프트당 하나의 엔진 생성기와 응답 슬롯을 생성하여 인증된 API 클라이언트가 하나의 요청으로 CPU, 메모리, 비동기 예약 용량, 엔진 요청 슬롯 및 응답 버퍼링을 소진할 수 있도록 합니다. 이 문제는 버전 0.26.0에서 해결되었습니다.</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>20260817205333</t>
+          <t>20260817214713</t>
         </is>
       </c>
     </row>
